--- a/jpcore-r4/main/StructureDefinition-jp-medicationrange.xlsx
+++ b/jpcore-r4/main/StructureDefinition-jp-medicationrange.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="245" uniqueCount="113">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="245" uniqueCount="119">
   <si>
     <t>Property</t>
   </si>
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.1.2</t>
+    <t>1.2.0a</t>
   </si>
   <si>
     <t>Name</t>
@@ -266,7 +266,7 @@
 </t>
   </si>
   <si>
-    <t>ele-1:すべてのFHIR要素には、@valueまたは子供が必要です / All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
+    <t>ele-1:すべてのFHIR要素には、@valueまたは子要素が必要です / All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
 rng-2:存在する場合、低い値は高よりも低い値を持つものとします / If present, low SHALL have a lower value than high {low.empty() or high.empty() or (low &lt;= high)}</t>
   </si>
   <si>
@@ -331,11 +331,14 @@
     <t>Element.extension</t>
   </si>
   <si>
-    <t>ele-1:すべてのFHIR要素には、@valueまたは子供が必要です / All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
+    <t>ele-1:すべてのFHIR要素には、@valueまたは子要素が必要です / All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
 ext-1:両方ではなく、拡張または値[x]が必要です / Must have either extensions or value[x], not both {extension.exists() != value.exists()}</t>
   </si>
   <si>
     <t>Range.low</t>
+  </si>
+  <si>
+    <t>Y</t>
   </si>
   <si>
     <t xml:space="preserve">Quantity {http://jpfhir.jp/fhir/core/StructureDefinition/JP_MedicationSimpleQuantity}
@@ -345,23 +348,38 @@
     <t>薬剤の上限量</t>
   </si>
   <si>
-    <t>薬剤に関する数量と単位を定めた簡易データイプ</t>
-  </si>
-  <si>
-    <t>薬剤に関する簡易的な数量と単位を定めている。ValueおよびCodeを必須とし、comparatorは記述不可。単位についてはMERIT9医薬品単位略号の利用を推進している。(**SHOULD**)</t>
-  </si>
-  <si>
-    <t>ele-1:すべてのFHIR要素には、@valueまたは子供が必要です / All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
-qty-3:ユニットのコードが存在する場合、システムも存在するものとします / If a code for the unit is present, the system SHALL also be present {code.empty() or system.exists()}sqty-1:コンパレータは、単純なQuantityで使用されません / The comparator is not used on a SimpleQuantity {comparator.empty()}</t>
-  </si>
-  <si>
-    <t>SN (see also Range) or CQ</t>
-  </si>
-  <si>
-    <t>PQ, IVL&lt;PQ&gt;, MO, CO, depending on the values</t>
+    <t>低制限。境界は包括的です。 / The low limit. The boundary is inclusive.</t>
+  </si>
+  <si>
+    <t>低要素が欠落している場合、低境界は不明です。 / If the low element is missing, the low boundary is not known.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ele-1:すべてのFHIR要素には、@valueまたは子要素が必要です / All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
+</t>
+  </si>
+  <si>
+    <t>NR.1</t>
+  </si>
+  <si>
+    <t>./low</t>
   </si>
   <si>
     <t>Range.high</t>
+  </si>
+  <si>
+    <t>高制限 / High limit</t>
+  </si>
+  <si>
+    <t>高制限。境界は包括的です。 / The high limit. The boundary is inclusive.</t>
+  </si>
+  <si>
+    <t>高い要素が欠落している場合、高境界は不明です。 / If the high element is missing, the high boundary is not known.</t>
+  </si>
+  <si>
+    <t>NR.2</t>
+  </si>
+  <si>
+    <t>./high</t>
   </si>
 </sst>
 </file>
@@ -1170,19 +1188,19 @@
         <v>76</v>
       </c>
       <c r="J5" t="s" s="2">
-        <v>76</v>
+        <v>105</v>
       </c>
       <c r="K5" t="s" s="2">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="L5" t="s" s="2">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="M5" t="s" s="2">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="N5" t="s" s="2">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="O5" s="2"/>
       <c r="P5" t="s" s="2">
@@ -1241,24 +1259,24 @@
         <v>87</v>
       </c>
       <c r="AI5" t="s" s="2">
-        <v>82</v>
+        <v>76</v>
       </c>
       <c r="AJ5" t="s" s="2">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="AK5" t="s" s="2">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="AL5" t="s" s="2">
-        <v>111</v>
+        <v>112</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s" s="2">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="B6" t="s" s="2">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="C6" s="2"/>
       <c r="D6" t="s" s="2">
@@ -1278,19 +1296,19 @@
         <v>76</v>
       </c>
       <c r="J6" t="s" s="2">
-        <v>76</v>
+        <v>105</v>
       </c>
       <c r="K6" t="s" s="2">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="L6" t="s" s="2">
-        <v>107</v>
+        <v>114</v>
       </c>
       <c r="M6" t="s" s="2">
-        <v>107</v>
+        <v>115</v>
       </c>
       <c r="N6" t="s" s="2">
-        <v>108</v>
+        <v>116</v>
       </c>
       <c r="O6" s="2"/>
       <c r="P6" t="s" s="2">
@@ -1340,7 +1358,7 @@
         <v>76</v>
       </c>
       <c r="AF6" t="s" s="2">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="AG6" t="s" s="2">
         <v>77</v>
@@ -1349,16 +1367,16 @@
         <v>87</v>
       </c>
       <c r="AI6" t="s" s="2">
-        <v>82</v>
+        <v>76</v>
       </c>
       <c r="AJ6" t="s" s="2">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="AK6" t="s" s="2">
-        <v>110</v>
+        <v>117</v>
       </c>
       <c r="AL6" t="s" s="2">
-        <v>111</v>
+        <v>118</v>
       </c>
     </row>
   </sheetData>

--- a/jpcore-r4/main/StructureDefinition-jp-medicationrange.xlsx
+++ b/jpcore-r4/main/StructureDefinition-jp-medicationrange.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.2.0a</t>
+    <t>1.2.0-a</t>
   </si>
   <si>
     <t>Name</t>

--- a/jpcore-r4/main/StructureDefinition-jp-medicationrange.xlsx
+++ b/jpcore-r4/main/StructureDefinition-jp-medicationrange.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.2.0-a</t>
+    <t>1.2.0</t>
   </si>
   <si>
     <t>Name</t>

--- a/jpcore-r4/main/StructureDefinition-jp-medicationrange.xlsx
+++ b/jpcore-r4/main/StructureDefinition-jp-medicationrange.xlsx
@@ -686,43 +686,43 @@
   <dimension ref="A1:AL6"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
-    <col min="1" max="1" width="16.44921875" customWidth="true" bestFit="true"/>
-    <col min="2" max="2" width="16.44921875" customWidth="true" bestFit="true"/>
-    <col min="3" max="3" width="12.66015625" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="4" max="4" width="12.64453125" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="5" max="5" width="6.77734375" customWidth="true" bestFit="true"/>
-    <col min="6" max="6" width="4.9453125" customWidth="true" bestFit="true"/>
-    <col min="7" max="7" width="5.4296875" customWidth="true" bestFit="true"/>
-    <col min="8" max="8" width="16.27734375" customWidth="true" bestFit="true"/>
-    <col min="9" max="9" width="13.26171875" customWidth="true" bestFit="true"/>
+    <col min="1" max="1" width="14.1015625" customWidth="true" bestFit="true"/>
+    <col min="2" max="2" width="14.1015625" customWidth="true" bestFit="true"/>
+    <col min="3" max="3" width="10.8515625" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="4" max="4" width="10.83984375" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="5" max="5" width="5.80859375" customWidth="true" bestFit="true"/>
+    <col min="6" max="6" width="4.23828125" customWidth="true" bestFit="true"/>
+    <col min="7" max="7" width="4.65625" customWidth="true" bestFit="true"/>
+    <col min="8" max="8" width="13.953125" customWidth="true" bestFit="true"/>
+    <col min="9" max="9" width="11.3671875" customWidth="true" bestFit="true"/>
     <col min="10" max="10" width="20.703125" customWidth="true" bestFit="true"/>
-    <col min="11" max="11" width="78.26953125" customWidth="true" bestFit="true"/>
+    <col min="11" max="11" width="67.1015625" customWidth="true" bestFit="true"/>
     <col min="12" max="12" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="13" max="13" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="14" max="14" width="100.703125" customWidth="true" bestFit="true"/>
-    <col min="15" max="15" width="15.6640625" customWidth="true" bestFit="true"/>
+    <col min="15" max="15" width="13.4296875" customWidth="true" bestFit="true"/>
     <col min="16" max="16" width="20.703125" customWidth="true" bestFit="true"/>
     <col min="17" max="17" width="20.703125" customWidth="true" bestFit="true"/>
     <col min="18" max="18" width="20.703125" customWidth="true" bestFit="true"/>
     <col min="19" max="19" width="20.703125" customWidth="true" bestFit="true"/>
-    <col min="20" max="20" width="9.953125" customWidth="true" bestFit="true"/>
-    <col min="21" max="21" width="17.171875" customWidth="true" bestFit="true"/>
-    <col min="22" max="22" width="17.65625" customWidth="true" bestFit="true"/>
-    <col min="23" max="23" width="19.03515625" customWidth="true" bestFit="true"/>
-    <col min="24" max="24" width="18.859375" customWidth="true" bestFit="true"/>
-    <col min="25" max="25" width="21.57421875" customWidth="true" bestFit="true"/>
-    <col min="26" max="26" width="19.625" customWidth="true" bestFit="true"/>
-    <col min="27" max="27" width="6.34765625" customWidth="true" bestFit="true"/>
-    <col min="28" max="28" width="22.71875" customWidth="true" bestFit="true"/>
-    <col min="29" max="29" width="42.03515625" customWidth="true" bestFit="true"/>
-    <col min="30" max="30" width="17.21484375" customWidth="true" bestFit="true"/>
-    <col min="31" max="31" width="14.4140625" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="32" max="32" width="18.1875" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="33" max="33" width="10.5546875" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="34" max="34" width="11.0390625" customWidth="true" bestFit="true"/>
+    <col min="20" max="20" width="8.53515625" customWidth="true" bestFit="true"/>
+    <col min="21" max="21" width="14.72265625" customWidth="true" bestFit="true"/>
+    <col min="22" max="22" width="15.13671875" customWidth="true" bestFit="true"/>
+    <col min="23" max="23" width="16.3203125" customWidth="true" bestFit="true"/>
+    <col min="24" max="24" width="16.16796875" customWidth="true" bestFit="true"/>
+    <col min="25" max="25" width="18.49609375" customWidth="true" bestFit="true"/>
+    <col min="26" max="26" width="16.828125" customWidth="true" bestFit="true"/>
+    <col min="27" max="27" width="5.44140625" customWidth="true" bestFit="true"/>
+    <col min="28" max="28" width="19.4765625" customWidth="true" bestFit="true"/>
+    <col min="29" max="29" width="36.0390625" customWidth="true" bestFit="true"/>
+    <col min="30" max="30" width="14.7578125" customWidth="true" bestFit="true"/>
+    <col min="31" max="31" width="12.359375" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="32" max="32" width="15.59375" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="33" max="33" width="9.046875" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="34" max="34" width="9.46484375" customWidth="true" bestFit="true"/>
     <col min="35" max="35" width="100.703125" customWidth="true"/>
-    <col min="37" max="37" width="44.546875" customWidth="true" bestFit="true"/>
-    <col min="38" max="38" width="94.8359375" customWidth="true" bestFit="true"/>
+    <col min="37" max="37" width="38.19140625" customWidth="true" bestFit="true"/>
+    <col min="38" max="38" width="81.3046875" customWidth="true" bestFit="true"/>
   </cols>
   <sheetData>
     <row r="1">

--- a/jpcore-r4/main/StructureDefinition-jp-medicationrange.xlsx
+++ b/jpcore-r4/main/StructureDefinition-jp-medicationrange.xlsx
@@ -90,7 +90,7 @@
     <t>Copyright</t>
   </si>
   <si>
-    <t>Copyright FHIR Japanese implementation research working group in Japan Association of Medical Informatics (JAMI) 一般社団法人日本医療情報学会NeXEHRS課題研究会FHIR日本実装検討WG</t>
+    <t>Copyright Japan FHIR Implementation Infrastructure Study Group in Japan Association of Medical Informatics (JAMI) 一般社団法人日本医療情報学会FHIR国内実装基盤研究会</t>
   </si>
   <si>
     <t>FHIR Version</t>
